--- a/bin/Debug/net9.0-windows/Template.xlsx
+++ b/bin/Debug/net9.0-windows/Template.xlsx
@@ -1,125 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29304"/>
-  <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programacion\Ritrama2025\bin\Debug\net9.0-windows\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E50E82-2AE2-4E54-9CA4-A2E6683ACED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="4170" yWindow="4950" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="TemplateMateriaPrima" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="0"/>
-</workbook>
+<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:workbookPr codeName="ThisWorkbook"/>
+  <x:bookViews>
+    <x:workbookView firstSheet="0" activeTab="0"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="TemplateMateriaPrima" sheetId="1" r:id="rId2"/>
+  </x:sheets>
+  <x:definedNames/>
+  <x:calcPr calcId="125725"/>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
-  <si>
-    <t>Product. Id.</t>
-  </si>
-  <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Width</t>
-  </si>
-  <si>
-    <t>Length</t>
-  </si>
-  <si>
-    <t>Msi</t>
-  </si>
-  <si>
-    <t>Core</t>
-  </si>
-  <si>
-    <t>Slipce</t>
-  </si>
-  <si>
-    <t>Roll-Id</t>
-  </si>
-  <si>
-    <t>01806</t>
-  </si>
-  <si>
-    <t>01837</t>
-  </si>
-  <si>
-    <t>GLOSS GOLD AP904 WG62</t>
-  </si>
-  <si>
-    <t>THERMAL TOP HS AR805 YG60 (DT ADHESIVE REMOVIBLE)</t>
-  </si>
-  <si>
-    <t>MASTER</t>
-  </si>
-  <si>
-    <t>01867</t>
-  </si>
-  <si>
-    <t>COATED 80 AP904 YG60</t>
-  </si>
-</sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t>Product. Id.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nombre del Producto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Roll-Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Width</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Length</x:t>
+  </x:si>
+  <x:si>
+    <x:t># Empalme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fecha Produccion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Factura</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ubicacion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palet #</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fecha de Llegada</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-  </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-  </fills>
-  <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-  </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
-</styleSheet>
+<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="2">
+    <x:numFmt numFmtId="0" formatCode=""/>
+    <x:numFmt numFmtId="164" formatCode="@"/>
+  </x:numFmts>
+  <x:fonts count="2">
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+  </x:fonts>
+  <x:fills count="3">
+    <x:fill>
+      <x:patternFill patternType="none"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD3D3D3"/>
+      </x:patternFill>
+    </x:fill>
+  </x:fills>
+  <x:borders count="1">
+    <x:border diagonalUp="0" diagonalDown="0">
+      <x:left style="none">
+        <x:color rgb="FF000000"/>
+      </x:left>
+      <x:right style="none">
+        <x:color rgb="FF000000"/>
+      </x:right>
+      <x:top style="none">
+        <x:color rgb="FF000000"/>
+      </x:top>
+      <x:bottom style="none">
+        <x:color rgb="FF000000"/>
+      </x:bottom>
+      <x:diagonal style="none">
+        <x:color rgb="FF000000"/>
+      </x:diagonal>
+    </x:border>
+  </x:borders>
+  <x:cellStyleXfs count="4">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+  </x:cellStyleXfs>
+  <x:cellXfs count="6">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+  </x:cellXfs>
+  <x:cellStyles count="1">
+    <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </x:cellStyles>
+</x:styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -406,138 +436,61 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.28515625" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" customWidth="1"/>
-    <col min="6" max="6" width="4.140625" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2">
-        <v>32</v>
-      </c>
-      <c r="E2">
-        <v>28000</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>12905044</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>24</v>
-      </c>
-      <c r="E3">
-        <v>32000</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>12905045</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4">
-        <v>18</v>
-      </c>
-      <c r="E4">
-        <v>27000</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>12905046</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-</worksheet>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K1"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="15.710625" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="50.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="6" width="15.710625" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="25.710625" style="1" customWidth="1"/>
+    <x:col min="8" max="10" width="12.710625" style="1" customWidth="1"/>
+    <x:col min="11" max="11" width="25.710625" style="1" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11" s="3" customFormat="1">
+      <x:c r="A1" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="5" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="5" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>